--- a/file/Real_time_Hub_Web_VPATJ13172.xlsx
+++ b/file/Real_time_Hub_Web_VPATJ13172.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{961685E7-FFD1-451E-9F14-F3BEC4E920EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BB396E9-0B83-45CE-A2B2-A2DB63A3D2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{50015E7C-BC68-4213-A2F0-1FFF8E3E6475}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E78D428A-B304-4C61-88E3-9971A3B77B3E}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年9月15日</t>
+    <t>作成日：2025年9月26日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1933,8 +1933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28457A0-96C6-40DC-A006-1309E6C8841F}">
-  <sheetPr codeName="Sheet309">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890AAE78-3FB2-4B5B-A940-7010E752BA72}">
+  <sheetPr codeName="Sheet349">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2749,7 +2749,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{5B57AACA-2C8C-4D58-8899-B5108DD1F505}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{221504BB-2E34-4575-9E99-786588B8CCAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2757,7 +2757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40770144-0B08-4B80-AF28-E4DF3B2FE8EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C6D50C-5454-4E7E-8CCA-0043FCF1160F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
